--- a/data/trans_orig/P11_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P11_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2007</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52868</t>
+          <t>52745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82804</t>
+          <t>80480</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77023</t>
+          <t>76566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108193</t>
+          <t>107013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>137885</t>
+          <t>136715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180899</t>
+          <t>180751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190206</t>
+          <t>192530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220142</t>
+          <t>220265</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152645</t>
+          <t>153825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183815</t>
+          <t>184272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>352949</t>
+          <t>353097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>395963</t>
+          <t>397133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88933</t>
+          <t>88590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128439</t>
+          <t>125970</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>188689</t>
+          <t>191655</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233349</t>
+          <t>232819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>288505</t>
+          <t>286856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>347420</t>
+          <t>348163</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364636</t>
+          <t>367105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404142</t>
+          <t>404485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270600</t>
+          <t>271130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>315260</t>
+          <t>312294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>649604</t>
+          <t>648861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>708519</t>
+          <t>710168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31337</t>
+          <t>31236</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54250</t>
+          <t>55679</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73752</t>
+          <t>75684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106140</t>
+          <t>107503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112782</t>
+          <t>109953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154814</t>
+          <t>152907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>264596</t>
+          <t>263167</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287509</t>
+          <t>287610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>229272</t>
+          <t>227909</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>261660</t>
+          <t>259728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>499444</t>
+          <t>501351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>541476</t>
+          <t>544305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60277</t>
+          <t>59569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93138</t>
+          <t>90007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111271</t>
+          <t>112434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147828</t>
+          <t>148861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181763</t>
+          <t>179884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233023</t>
+          <t>227982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>265533</t>
+          <t>268664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298394</t>
+          <t>299102</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223628</t>
+          <t>222595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>260185</t>
+          <t>259022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>497104</t>
+          <t>502145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>548364</t>
+          <t>550243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22309</t>
+          <t>22267</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40901</t>
+          <t>43460</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35638</t>
+          <t>36946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61435</t>
+          <t>61768</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64180</t>
+          <t>64050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96541</t>
+          <t>94870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162407</t>
+          <t>159848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180999</t>
+          <t>181041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>146233</t>
+          <t>145900</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>172030</t>
+          <t>170722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>314435</t>
+          <t>316106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>346796</t>
+          <t>346926</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>40485</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65207</t>
+          <t>63732</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66464</t>
+          <t>68962</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98477</t>
+          <t>99018</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115349</t>
+          <t>114628</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154794</t>
+          <t>154084</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>205604</t>
+          <t>207079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231494</t>
+          <t>230326</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179667</t>
+          <t>179126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>211680</t>
+          <t>209182</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>394161</t>
+          <t>394871</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>433606</t>
+          <t>434327</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68768</t>
+          <t>70553</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103415</t>
+          <t>103279</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112023</t>
+          <t>111547</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152699</t>
+          <t>152000</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190318</t>
+          <t>191302</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247073</t>
+          <t>246281</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>511612</t>
+          <t>511748</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>546259</t>
+          <t>544474</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>485520</t>
+          <t>486219</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>526196</t>
+          <t>526672</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1006173</t>
+          <t>1006965</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1062928</t>
+          <t>1061944</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119084</t>
+          <t>118202</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>160119</t>
+          <t>162606</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>179698</t>
+          <t>180067</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>227126</t>
+          <t>229286</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>309406</t>
+          <t>308739</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>373418</t>
+          <t>374636</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>583676</t>
+          <t>581189</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>624711</t>
+          <t>625593</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>556385</t>
+          <t>554225</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>603813</t>
+          <t>603444</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1153888</t>
+          <t>1152670</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1217900</t>
+          <t>1218567</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>552983</t>
+          <t>554337</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>642865</t>
+          <t>643076</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>931344</t>
+          <t>933971</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1036340</t>
+          <t>1042379</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1514374</t>
+          <t>1510899</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1655188</t>
+          <t>1649700</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2633678</t>
+          <t>2633467</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2723560</t>
+          <t>2722206</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2342857</t>
+          <t>2336818</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2447853</t>
+          <t>2445226</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5000553</t>
+          <t>5006041</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5141367</t>
+          <t>5144842</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2012</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46690</t>
+          <t>47068</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75649</t>
+          <t>74666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87404</t>
+          <t>88076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123645</t>
+          <t>122505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144352</t>
+          <t>145077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188175</t>
+          <t>187669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216011</t>
+          <t>216994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244970</t>
+          <t>244592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162661</t>
+          <t>163801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198902</t>
+          <t>198230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>389791</t>
+          <t>390297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>433614</t>
+          <t>432889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,9%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56137</t>
+          <t>56781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92717</t>
+          <t>91484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132362</t>
+          <t>132413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174629</t>
+          <t>176267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195006</t>
+          <t>198874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250380</t>
+          <t>253679</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411863</t>
+          <t>413096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448443</t>
+          <t>447799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349136</t>
+          <t>347498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>391403</t>
+          <t>391352</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>777965</t>
+          <t>774666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>833339</t>
+          <t>829471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38264</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67099</t>
+          <t>68021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74326</t>
+          <t>73589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106884</t>
+          <t>108065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120085</t>
+          <t>122880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163463</t>
+          <t>164683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256947</t>
+          <t>256025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285782</t>
+          <t>285179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234136</t>
+          <t>232955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>266694</t>
+          <t>267431</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>501603</t>
+          <t>500383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>544981</t>
+          <t>542186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47356</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76239</t>
+          <t>79141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115705</t>
+          <t>116355</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153270</t>
+          <t>153460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171997</t>
+          <t>173760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220699</t>
+          <t>223456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291574</t>
+          <t>288672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320457</t>
+          <t>317318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>233727</t>
+          <t>233537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>271292</t>
+          <t>270642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>534110</t>
+          <t>531353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>582812</t>
+          <t>581049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34430</t>
+          <t>34043</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59393</t>
+          <t>59097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86268</t>
+          <t>87685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116041</t>
+          <t>117670</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128800</t>
+          <t>127305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167627</t>
+          <t>167846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153225</t>
+          <t>153521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178188</t>
+          <t>178575</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103550</t>
+          <t>101921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133323</t>
+          <t>131906</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264582</t>
+          <t>264363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>303409</t>
+          <t>304904</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>53339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81449</t>
+          <t>81538</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66581</t>
+          <t>65963</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97325</t>
+          <t>95583</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128924</t>
+          <t>130523</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172995</t>
+          <t>170224</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>191664</t>
+          <t>191575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>218760</t>
+          <t>219774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>182706</t>
+          <t>184448</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>213450</t>
+          <t>214068</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>380149</t>
+          <t>382920</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>424220</t>
+          <t>422621</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81221</t>
+          <t>81823</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120259</t>
+          <t>119338</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162878</t>
+          <t>161018</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211901</t>
+          <t>210223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>254392</t>
+          <t>257422</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>318402</t>
+          <t>321159</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>541576</t>
+          <t>542497</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>580614</t>
+          <t>580012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>480980</t>
+          <t>482658</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>530003</t>
+          <t>531863</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1036314</t>
+          <t>1033557</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1100324</t>
+          <t>1097294</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,0%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>160598</t>
+          <t>160972</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>211419</t>
+          <t>212677</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>235205</t>
+          <t>235679</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>291914</t>
+          <t>291091</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>412314</t>
+          <t>412743</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>492350</t>
+          <t>488327</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>562603</t>
+          <t>561345</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>613424</t>
+          <t>613050</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>531939</t>
+          <t>532762</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>588648</t>
+          <t>588174</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1105525</t>
+          <t>1109548</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1185561</t>
+          <t>1185132</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>596618</t>
+          <t>597889</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>691523</t>
+          <t>692568</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1056150</t>
+          <t>1059235</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1177238</t>
+          <t>1173836</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1684174</t>
+          <t>1681452</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1834398</t>
+          <t>1828983</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2718164</t>
+          <t>2717119</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2813069</t>
+          <t>2811798</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2377206</t>
+          <t>2380608</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2498294</t>
+          <t>2495209</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5129733</t>
+          <t>5135148</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5279957</t>
+          <t>5282679</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2016</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46268</t>
+          <t>46547</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74845</t>
+          <t>74495</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92706</t>
+          <t>91398</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126840</t>
+          <t>125554</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145580</t>
+          <t>146440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190601</t>
+          <t>191139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214651</t>
+          <t>215001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243228</t>
+          <t>242949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>160012</t>
+          <t>161298</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194146</t>
+          <t>195454</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>385748</t>
+          <t>385210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>430769</t>
+          <t>429909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51823</t>
+          <t>51273</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81978</t>
+          <t>80495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94005</t>
+          <t>93280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133215</t>
+          <t>133247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154428</t>
+          <t>153589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>202433</t>
+          <t>205552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420597</t>
+          <t>422080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>450752</t>
+          <t>451302</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>386631</t>
+          <t>386599</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>425841</t>
+          <t>426566</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>819989</t>
+          <t>816870</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>867994</t>
+          <t>868833</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31537</t>
+          <t>31625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54430</t>
+          <t>53168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58815</t>
+          <t>61776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90978</t>
+          <t>93492</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97410</t>
+          <t>98779</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137924</t>
+          <t>136978</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>261461</t>
+          <t>262723</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284354</t>
+          <t>284266</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>240229</t>
+          <t>237715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>272392</t>
+          <t>269431</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>509174</t>
+          <t>510120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>549688</t>
+          <t>548319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67106</t>
+          <t>66308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99040</t>
+          <t>98840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124402</t>
+          <t>125077</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164514</t>
+          <t>165978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>201175</t>
+          <t>200725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250923</t>
+          <t>251421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268909</t>
+          <t>269109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300843</t>
+          <t>301641</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219731</t>
+          <t>218267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259843</t>
+          <t>259168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>501271</t>
+          <t>500773</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>551019</t>
+          <t>551469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,31%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34484</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58789</t>
+          <t>59042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>50892</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78153</t>
+          <t>78539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91048</t>
+          <t>92685</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127288</t>
+          <t>128927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147676</t>
+          <t>147423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171981</t>
+          <t>172318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140434</t>
+          <t>140048</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166867</t>
+          <t>167695</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>297764</t>
+          <t>296125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>334004</t>
+          <t>332367</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46477</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74235</t>
+          <t>71969</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68100</t>
+          <t>68633</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99591</t>
+          <t>100141</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122737</t>
+          <t>121151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163212</t>
+          <t>162354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188888</t>
+          <t>191154</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216646</t>
+          <t>217848</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>171389</t>
+          <t>170839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>202880</t>
+          <t>202347</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>370891</t>
+          <t>371749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>411366</t>
+          <t>412952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129339</t>
+          <t>129139</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>172894</t>
+          <t>173210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>192827</t>
+          <t>189866</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>243133</t>
+          <t>240631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>331393</t>
+          <t>331833</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398715</t>
+          <t>400248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>476766</t>
+          <t>476450</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>520321</t>
+          <t>520521</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>445033</t>
+          <t>447535</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>495339</t>
+          <t>498300</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>939111</t>
+          <t>937578</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1006433</t>
+          <t>1005993</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>103697</t>
+          <t>103140</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>144259</t>
+          <t>143833</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>184597</t>
+          <t>186481</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>242326</t>
+          <t>239055</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>299730</t>
+          <t>303088</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>369190</t>
+          <t>369811</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>630212</t>
+          <t>630638</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>670774</t>
+          <t>671331</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>579779</t>
+          <t>583050</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>637508</t>
+          <t>635624</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1227386</t>
+          <t>1226765</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1296846</t>
+          <t>1293488</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>584514</t>
+          <t>583392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>670850</t>
+          <t>675663</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>963266</t>
+          <t>959073</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1073617</t>
+          <t>1071321</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1567702</t>
+          <t>1576319</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1716472</t>
+          <t>1720911</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2698780</t>
+          <t>2693967</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2785116</t>
+          <t>2786238</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2448372</t>
+          <t>2450668</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2558723</t>
+          <t>2562916</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5175146</t>
+          <t>5170707</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5323916</t>
+          <t>5315299</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2023</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73158</t>
+          <t>73545</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110083</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130539</t>
+          <t>131476</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>159740</t>
+          <t>160235</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>215188</t>
+          <t>213678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>262672</t>
+          <t>260388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,32%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>201360</t>
+          <t>199924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238285</t>
+          <t>237898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129895</t>
+          <t>129400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>159096</t>
+          <t>158159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>338405</t>
+          <t>340689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>385889</t>
+          <t>387399</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100481</t>
+          <t>97906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143628</t>
+          <t>144015</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159068</t>
+          <t>160517</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>197853</t>
+          <t>197495</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>271816</t>
+          <t>269480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>329277</t>
+          <t>329199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374762</t>
+          <t>374375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417909</t>
+          <t>420484</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317116</t>
+          <t>317474</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355901</t>
+          <t>354452</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704082</t>
+          <t>704160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>761543</t>
+          <t>763879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88350</t>
+          <t>87074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119205</t>
+          <t>119751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112991</t>
+          <t>112433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143627</t>
+          <t>141761</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>210509</t>
+          <t>209006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254632</t>
+          <t>251495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196845</t>
+          <t>196299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227700</t>
+          <t>228976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205501</t>
+          <t>207367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>236137</t>
+          <t>236695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>410546</t>
+          <t>413683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>454669</t>
+          <t>456172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78488</t>
+          <t>78759</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118124</t>
+          <t>115557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97103</t>
+          <t>101294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207840</t>
+          <t>207197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184167</t>
+          <t>190267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>306324</t>
+          <t>302812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193017</t>
+          <t>195584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>232653</t>
+          <t>232382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267420</t>
+          <t>268063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378157</t>
+          <t>373966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>480077</t>
+          <t>483589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>602234</t>
+          <t>596134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34730</t>
+          <t>33880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51959</t>
+          <t>51645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60570</t>
+          <t>60889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78833</t>
+          <t>79107</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99603</t>
+          <t>99394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124764</t>
+          <t>124479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126783</t>
+          <t>127097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144012</t>
+          <t>144862</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129390</t>
+          <t>129116</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147653</t>
+          <t>147334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>262201</t>
+          <t>262486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>287362</t>
+          <t>287571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104077</t>
+          <t>104363</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132572</t>
+          <t>132622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126765</t>
+          <t>127633</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>153581</t>
+          <t>153419</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>238424</t>
+          <t>238171</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>277924</t>
+          <t>275755</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137064</t>
+          <t>137014</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>165559</t>
+          <t>165273</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103475</t>
+          <t>103637</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>130291</t>
+          <t>129423</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>248768</t>
+          <t>250937</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>288268</t>
+          <t>288521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139097</t>
+          <t>139492</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187974</t>
+          <t>188731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>291251</t>
+          <t>289305</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>641102</t>
+          <t>641209</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>441083</t>
+          <t>440996</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>930988</t>
+          <t>922056</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>435574</t>
+          <t>434817</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>484451</t>
+          <t>484056</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>206406</t>
+          <t>206299</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>556257</t>
+          <t>558203</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>540069</t>
+          <t>549001</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1029974</t>
+          <t>1030061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54094</t>
+          <t>56310</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178518</t>
+          <t>178554</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>191577</t>
+          <t>191631</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>234729</t>
+          <t>234660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>207052</t>
+          <t>189927</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>407041</t>
+          <t>405205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>749286</t>
+          <t>749250</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>873710</t>
+          <t>871494</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>481752</t>
+          <t>481821</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>524904</t>
+          <t>524850</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1237245</t>
+          <t>1239081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1437234</t>
+          <t>1454359</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>676549</t>
+          <t>670918</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>949686</t>
+          <t>946553</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1309506</t>
+          <t>1314973</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1857299</t>
+          <t>1891058</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2109118</t>
+          <t>2109545</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2856413</t>
+          <t>2774079</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -13554,17 +13554,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2596949</t>
+          <t>2596950</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2507068</t>
+          <t>2510202</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2780205</t>
+          <t>2785837</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1800960</t>
+          <t>1767201</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2348753</t>
+          <t>2343286</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4258600</t>
+          <t>4340934</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5005895</t>
+          <t>5005468</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,35%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">

--- a/data/trans_orig/P11_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P11_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52745</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80480</t>
+          <t>80758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76566</t>
+          <t>76655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107013</t>
+          <t>108682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136715</t>
+          <t>136949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180751</t>
+          <t>181378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>192530</t>
+          <t>192252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220265</t>
+          <t>221627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>153825</t>
+          <t>152156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184272</t>
+          <t>184183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>353097</t>
+          <t>352470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>397133</t>
+          <t>396899</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88590</t>
+          <t>89392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125970</t>
+          <t>126175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>191655</t>
+          <t>190692</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>232819</t>
+          <t>232468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>286856</t>
+          <t>291263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>348163</t>
+          <t>347261</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367105</t>
+          <t>366900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404485</t>
+          <t>403683</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>271130</t>
+          <t>271481</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>312294</t>
+          <t>313257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>648861</t>
+          <t>649763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710168</t>
+          <t>705761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31236</t>
+          <t>30772</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55679</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75684</t>
+          <t>75652</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107503</t>
+          <t>107967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109953</t>
+          <t>111669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152907</t>
+          <t>152148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>263167</t>
+          <t>265639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287610</t>
+          <t>288074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227909</t>
+          <t>227445</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259728</t>
+          <t>259760</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>501351</t>
+          <t>502110</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>544305</t>
+          <t>542589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>58624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90007</t>
+          <t>90887</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112434</t>
+          <t>114130</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148861</t>
+          <t>147878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179884</t>
+          <t>182056</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227982</t>
+          <t>228491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268664</t>
+          <t>267784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299102</t>
+          <t>300047</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222595</t>
+          <t>223578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259022</t>
+          <t>257326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>502145</t>
+          <t>501636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>550243</t>
+          <t>548071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22267</t>
+          <t>21834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43460</t>
+          <t>41261</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>36825</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61768</t>
+          <t>60674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64050</t>
+          <t>64407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94870</t>
+          <t>96778</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159848</t>
+          <t>162047</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181041</t>
+          <t>181474</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145900</t>
+          <t>146994</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170722</t>
+          <t>170843</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>316106</t>
+          <t>314198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>346926</t>
+          <t>346569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40485</t>
+          <t>39617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63732</t>
+          <t>65962</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68962</t>
+          <t>67770</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99018</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114628</t>
+          <t>115272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154084</t>
+          <t>154968</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207079</t>
+          <t>204849</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230326</t>
+          <t>231194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179126</t>
+          <t>180317</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209182</t>
+          <t>210374</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>394871</t>
+          <t>393987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>434327</t>
+          <t>433683</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70553</t>
+          <t>69942</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103279</t>
+          <t>104059</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111547</t>
+          <t>112577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152000</t>
+          <t>151701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191302</t>
+          <t>190211</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>246281</t>
+          <t>242311</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>511748</t>
+          <t>510968</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>544474</t>
+          <t>545085</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>486219</t>
+          <t>486518</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>526672</t>
+          <t>525642</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1006965</t>
+          <t>1010935</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1061944</t>
+          <t>1063035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118202</t>
+          <t>118905</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162606</t>
+          <t>161480</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>180067</t>
+          <t>178635</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>229286</t>
+          <t>230064</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>308739</t>
+          <t>310583</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>374636</t>
+          <t>374583</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>581189</t>
+          <t>582315</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>625593</t>
+          <t>624890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>554225</t>
+          <t>553447</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>603444</t>
+          <t>604876</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1152670</t>
+          <t>1152723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1218567</t>
+          <t>1216723</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,66%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>554337</t>
+          <t>553244</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>643076</t>
+          <t>639974</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>933971</t>
+          <t>938814</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1042379</t>
+          <t>1044684</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1510899</t>
+          <t>1508456</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1649700</t>
+          <t>1648796</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2633467</t>
+          <t>2636569</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2722206</t>
+          <t>2723299</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2336818</t>
+          <t>2334513</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2445226</t>
+          <t>2440383</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5006041</t>
+          <t>5006945</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5144842</t>
+          <t>5147285</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47068</t>
+          <t>47473</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74666</t>
+          <t>75026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88076</t>
+          <t>88863</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122505</t>
+          <t>123342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145077</t>
+          <t>142952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>187669</t>
+          <t>191638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216994</t>
+          <t>216634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244592</t>
+          <t>244187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>163801</t>
+          <t>162964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198230</t>
+          <t>197443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>390297</t>
+          <t>386328</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>432889</t>
+          <t>435014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,27%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56781</t>
+          <t>56637</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91484</t>
+          <t>92063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132413</t>
+          <t>130693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176267</t>
+          <t>174710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198874</t>
+          <t>198095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>253679</t>
+          <t>252949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413096</t>
+          <t>412517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447799</t>
+          <t>447943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>347498</t>
+          <t>349055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>391352</t>
+          <t>393072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>774666</t>
+          <t>775396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>829471</t>
+          <t>830250</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38867</t>
+          <t>39179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68021</t>
+          <t>66168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73589</t>
+          <t>73255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108065</t>
+          <t>106835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122880</t>
+          <t>120516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164683</t>
+          <t>165456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256025</t>
+          <t>257878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285179</t>
+          <t>284867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232955</t>
+          <t>234185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>267431</t>
+          <t>267765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>500383</t>
+          <t>499610</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>542186</t>
+          <t>544550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50495</t>
+          <t>47350</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79141</t>
+          <t>78247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116355</t>
+          <t>116580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153460</t>
+          <t>153865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173760</t>
+          <t>172453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>223456</t>
+          <t>221433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288672</t>
+          <t>289566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317318</t>
+          <t>320463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>233537</t>
+          <t>233132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>270642</t>
+          <t>270417</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>531353</t>
+          <t>533376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>581049</t>
+          <t>582356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>35231</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59097</t>
+          <t>58786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87685</t>
+          <t>86964</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117670</t>
+          <t>117215</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127305</t>
+          <t>127744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167846</t>
+          <t>167249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153521</t>
+          <t>153832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178575</t>
+          <t>177387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101921</t>
+          <t>102376</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131906</t>
+          <t>132627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264363</t>
+          <t>264960</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>304904</t>
+          <t>304465</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53339</t>
+          <t>54145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81538</t>
+          <t>82890</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>67668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95583</t>
+          <t>96947</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130523</t>
+          <t>128514</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170224</t>
+          <t>170415</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>191575</t>
+          <t>190223</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219774</t>
+          <t>218968</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184448</t>
+          <t>183084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214068</t>
+          <t>212363</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>382920</t>
+          <t>382729</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>422621</t>
+          <t>424630</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81823</t>
+          <t>82113</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119338</t>
+          <t>121629</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161018</t>
+          <t>159767</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>210223</t>
+          <t>211240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257422</t>
+          <t>253881</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>321159</t>
+          <t>317473</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>542497</t>
+          <t>540206</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>580012</t>
+          <t>579722</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>482658</t>
+          <t>481641</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>531863</t>
+          <t>533114</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1033557</t>
+          <t>1037243</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1097294</t>
+          <t>1100835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,26%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>160972</t>
+          <t>162954</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>212677</t>
+          <t>210847</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>235679</t>
+          <t>233821</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>291091</t>
+          <t>290079</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>412743</t>
+          <t>411181</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>488327</t>
+          <t>485702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>561345</t>
+          <t>563175</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>613050</t>
+          <t>611068</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>532762</t>
+          <t>533774</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>588174</t>
+          <t>590032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1109548</t>
+          <t>1112173</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1185132</t>
+          <t>1186694</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>597889</t>
+          <t>597213</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>692568</t>
+          <t>692784</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1059235</t>
+          <t>1054956</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1173836</t>
+          <t>1165572</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1681452</t>
+          <t>1686514</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1828983</t>
+          <t>1834573</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2717119</t>
+          <t>2716903</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2811798</t>
+          <t>2812474</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2380608</t>
+          <t>2388872</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2495209</t>
+          <t>2499488</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5135148</t>
+          <t>5129558</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5282679</t>
+          <t>5277617</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46547</t>
+          <t>45403</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74495</t>
+          <t>74424</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91398</t>
+          <t>92065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125554</t>
+          <t>125209</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146440</t>
+          <t>145815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191139</t>
+          <t>188776</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215001</t>
+          <t>215072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242949</t>
+          <t>244093</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161298</t>
+          <t>161643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195454</t>
+          <t>194787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>385210</t>
+          <t>387573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>429909</t>
+          <t>430534</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51273</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80495</t>
+          <t>79827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93280</t>
+          <t>94074</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133247</t>
+          <t>134784</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153589</t>
+          <t>152589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205552</t>
+          <t>203252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422080</t>
+          <t>422748</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451302</t>
+          <t>451298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>386599</t>
+          <t>385062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>426566</t>
+          <t>425772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>816870</t>
+          <t>819170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>868833</t>
+          <t>869833</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31625</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53168</t>
+          <t>55445</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>59883</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>92179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98779</t>
+          <t>99192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136978</t>
+          <t>138832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>262723</t>
+          <t>260446</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284266</t>
+          <t>283676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237715</t>
+          <t>239028</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269431</t>
+          <t>271324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>510120</t>
+          <t>508266</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>548319</t>
+          <t>547906</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66308</t>
+          <t>67403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98840</t>
+          <t>100159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>125077</t>
+          <t>122241</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165978</t>
+          <t>162713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200725</t>
+          <t>199748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>251421</t>
+          <t>251693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>269109</t>
+          <t>267790</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301641</t>
+          <t>300546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218267</t>
+          <t>221532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259168</t>
+          <t>262004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>500773</t>
+          <t>500501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>551469</t>
+          <t>552446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59042</t>
+          <t>57260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50892</t>
+          <t>50778</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78539</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92685</t>
+          <t>91333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128927</t>
+          <t>127071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147423</t>
+          <t>149205</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172318</t>
+          <t>172098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140048</t>
+          <t>141125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167695</t>
+          <t>167809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296125</t>
+          <t>297981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>332367</t>
+          <t>333719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71969</t>
+          <t>71615</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68633</t>
+          <t>68539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100141</t>
+          <t>98241</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121151</t>
+          <t>119667</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>162354</t>
+          <t>162452</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>191154</t>
+          <t>191508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>170839</t>
+          <t>172739</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>202347</t>
+          <t>202441</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371749</t>
+          <t>371651</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412952</t>
+          <t>414436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,59%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129139</t>
+          <t>128430</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173210</t>
+          <t>172595</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>189866</t>
+          <t>190784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>240631</t>
+          <t>243526</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>331833</t>
+          <t>333395</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>400248</t>
+          <t>402191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>476450</t>
+          <t>477065</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>520521</t>
+          <t>521230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>447535</t>
+          <t>444640</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>498300</t>
+          <t>497382</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>937578</t>
+          <t>935635</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1005993</t>
+          <t>1004431</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>103140</t>
+          <t>104008</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143833</t>
+          <t>144550</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>186481</t>
+          <t>186877</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>239055</t>
+          <t>238858</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>303088</t>
+          <t>304493</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>369811</t>
+          <t>374356</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>630638</t>
+          <t>629921</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>671331</t>
+          <t>670463</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>583050</t>
+          <t>583247</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>635624</t>
+          <t>635228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1226765</t>
+          <t>1222220</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1293488</t>
+          <t>1292083</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>583392</t>
+          <t>585906</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>675663</t>
+          <t>673772</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>959073</t>
+          <t>957490</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1071321</t>
+          <t>1065099</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1576319</t>
+          <t>1570059</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1720911</t>
+          <t>1711007</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2693967</t>
+          <t>2695858</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2786238</t>
+          <t>2783724</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2450668</t>
+          <t>2456890</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2562916</t>
+          <t>2564499</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5170707</t>
+          <t>5180611</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5315299</t>
+          <t>5321559</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91127</t>
+          <t>89913</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73545</t>
+          <t>76179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111519</t>
+          <t>106865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>145839</t>
+          <t>154836</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131476</t>
+          <t>138463</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>160235</t>
+          <t>169126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>236965</t>
+          <t>244750</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213678</t>
+          <t>224492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260388</t>
+          <t>266385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>220316</t>
+          <t>228932</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199924</t>
+          <t>211980</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237898</t>
+          <t>242666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>143796</t>
+          <t>161225</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129400</t>
+          <t>146935</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158159</t>
+          <t>177598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>364112</t>
+          <t>390156</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>340689</t>
+          <t>368521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>387399</t>
+          <t>410414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>120429</t>
+          <t>126195</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97906</t>
+          <t>104679</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144015</t>
+          <t>149716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>178783</t>
+          <t>187404</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160517</t>
+          <t>168565</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>197495</t>
+          <t>207991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>299211</t>
+          <t>313599</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>269480</t>
+          <t>284875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>329199</t>
+          <t>346334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>397961</t>
+          <t>404452</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374375</t>
+          <t>380931</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420484</t>
+          <t>425968</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>336186</t>
+          <t>359090</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317474</t>
+          <t>338503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354452</t>
+          <t>377929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>734148</t>
+          <t>763542</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704160</t>
+          <t>730807</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>763879</t>
+          <t>792266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>103064</t>
+          <t>105584</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87074</t>
+          <t>91202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119751</t>
+          <t>122853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>127741</t>
+          <t>131569</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112433</t>
+          <t>116470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141761</t>
+          <t>147357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>230806</t>
+          <t>237153</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>209006</t>
+          <t>215232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>251495</t>
+          <t>259553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>212986</t>
+          <t>210409</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196299</t>
+          <t>193140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>228976</t>
+          <t>224791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>221387</t>
+          <t>224812</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>207367</t>
+          <t>209024</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>236695</t>
+          <t>239911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>434372</t>
+          <t>435222</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>413683</t>
+          <t>412822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>456172</t>
+          <t>457143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>96855</t>
+          <t>109833</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78759</t>
+          <t>90221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115557</t>
+          <t>133325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>164605</t>
+          <t>182991</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101294</t>
+          <t>165958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207197</t>
+          <t>203641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>261460</t>
+          <t>292824</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190267</t>
+          <t>261475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302812</t>
+          <t>320845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>214286</t>
+          <t>261734</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195584</t>
+          <t>238242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>232382</t>
+          <t>281346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>310655</t>
+          <t>238489</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>268063</t>
+          <t>217839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>373966</t>
+          <t>255522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>524941</t>
+          <t>500223</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>483589</t>
+          <t>472202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>596134</t>
+          <t>531572</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>67,03%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311141</t>
+          <t>371567</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311141</t>
+          <t>371567</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311141</t>
+          <t>371567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475260</t>
+          <t>421480</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475260</t>
+          <t>421480</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475260</t>
+          <t>421480</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>786401</t>
+          <t>793047</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>786401</t>
+          <t>793047</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>786401</t>
+          <t>793047</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>42182</t>
+          <t>46345</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33880</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51645</t>
+          <t>56334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>69445</t>
+          <t>72089</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60889</t>
+          <t>63518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79107</t>
+          <t>81391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>111627</t>
+          <t>118434</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99394</t>
+          <t>105295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124479</t>
+          <t>132561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>136560</t>
+          <t>159320</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127097</t>
+          <t>149331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144862</t>
+          <t>168249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>138778</t>
+          <t>154660</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129116</t>
+          <t>145358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147334</t>
+          <t>163231</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>275338</t>
+          <t>313980</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>262486</t>
+          <t>299853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>287571</t>
+          <t>327119</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>75,65%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208223</t>
+          <t>226749</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208223</t>
+          <t>226749</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208223</t>
+          <t>226749</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386965</t>
+          <t>432414</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386965</t>
+          <t>432414</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386965</t>
+          <t>432414</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>117786</t>
+          <t>118278</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104363</t>
+          <t>104349</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132622</t>
+          <t>132552</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>140088</t>
+          <t>144384</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>127633</t>
+          <t>130328</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>153419</t>
+          <t>157474</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>257874</t>
+          <t>262661</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>238171</t>
+          <t>242048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>275755</t>
+          <t>281363</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>151850</t>
+          <t>152429</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137014</t>
+          <t>138155</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>165273</t>
+          <t>166358</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>116968</t>
+          <t>119366</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103637</t>
+          <t>106276</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>129423</t>
+          <t>133422</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>268818</t>
+          <t>271796</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>250937</t>
+          <t>253094</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>288521</t>
+          <t>292409</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>163401</t>
+          <t>193093</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139492</t>
+          <t>167922</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>188731</t>
+          <t>219438</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>430865</t>
+          <t>270983</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>289305</t>
+          <t>246262</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>641209</t>
+          <t>294467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>594266</t>
+          <t>464076</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>440996</t>
+          <t>428080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>922056</t>
+          <t>500110</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>460147</t>
+          <t>525590</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>434817</t>
+          <t>499245</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>484056</t>
+          <t>550761</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>416643</t>
+          <t>499070</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>206299</t>
+          <t>475586</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>558203</t>
+          <t>523791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>876791</t>
+          <t>1024659</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>549001</t>
+          <t>988625</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1030061</t>
+          <t>1060655</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>71,25%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623548</t>
+          <t>718683</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623548</t>
+          <t>718683</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623548</t>
+          <t>718683</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847508</t>
+          <t>770053</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847508</t>
+          <t>770053</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847508</t>
+          <t>770053</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1471057</t>
+          <t>1488735</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1471057</t>
+          <t>1488735</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1471057</t>
+          <t>1488735</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>124961</t>
+          <t>144071</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56310</t>
+          <t>124841</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178554</t>
+          <t>168710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>213366</t>
+          <t>240838</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>191631</t>
+          <t>218354</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>234660</t>
+          <t>262092</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>338328</t>
+          <t>384909</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>189927</t>
+          <t>358671</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>405205</t>
+          <t>418746</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>802843</t>
+          <t>652962</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>749250</t>
+          <t>628323</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>871494</t>
+          <t>672192</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>503115</t>
+          <t>588987</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>481821</t>
+          <t>567733</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>524850</t>
+          <t>611471</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1305958</t>
+          <t>1241948</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1239081</t>
+          <t>1208111</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1454359</t>
+          <t>1268186</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927804</t>
+          <t>797033</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927804</t>
+          <t>797033</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927804</t>
+          <t>797033</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716481</t>
+          <t>829825</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716481</t>
+          <t>829825</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716481</t>
+          <t>829825</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644286</t>
+          <t>1626857</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644286</t>
+          <t>1626857</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644286</t>
+          <t>1626857</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>859805</t>
+          <t>933312</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>670918</t>
+          <t>875133</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>946553</t>
+          <t>985944</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1470732</t>
+          <t>1385094</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1314973</t>
+          <t>1331342</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1891058</t>
+          <t>1435380</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2330537</t>
+          <t>2318406</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2109545</t>
+          <t>2244434</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2774079</t>
+          <t>2401930</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2596950</t>
+          <t>2595828</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2510202</t>
+          <t>2543196</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2785837</t>
+          <t>2654007</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2187527</t>
+          <t>2345700</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1767201</t>
+          <t>2295414</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2343286</t>
+          <t>2399452</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4784476</t>
+          <t>4941528</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4340934</t>
+          <t>4858004</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5005468</t>
+          <t>5015500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
